--- a/mvc/dist/SerenazgoTalara/unidades_registro.xlsx
+++ b/mvc/dist/SerenazgoTalara/unidades_registro.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Registro de Unidades" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -25,10 +26,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -44,8 +42,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2C3E50"/>
-        <bgColor rgb="FF2C3E50"/>
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
       </patternFill>
     </fill>
     <fill>
@@ -64,19 +62,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -84,7 +73,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -92,7 +81,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -455,18 +444,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col width="10.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="13.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="4" bestFit="1" customWidth="1" min="4" max="5"/>
-    <col width="3.5703125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="18.28515625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="13.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="41.28515625" bestFit="1" customWidth="1" min="9" max="9"/>
-  </cols>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -518,30 +497,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>03:14:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🚙 4 EUI-646</t>
+          <t>🚙 1 EUI-621</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>NOCHE, DÍA, TARDE</t>
@@ -549,45 +532,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>T.ALTA</t>
+          <t>SECTORIAL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FALTA 7 KM, COMPLETO, PO requerido</t>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>03:14:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🚙 5 EUI-685</t>
+          <t>🚙 2 EUI-682</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NOCHE, DÍA, TARDE</t>
+          <t>DÍA, TARDE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,40 +589,49 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FALTA 26 KM, COMPLETO, PO requerido</t>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>03:14:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🚙 8 EUI-680</t>
+          <t>🚙 3 EUI-683</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOCHE, DÍA, TARDE</t>
+          <t>NOCHE, TARDE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -640,80 +641,98 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FALTA 23 KM, COMPLETO, PO requerido</t>
+          <t>SUR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>03:14:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🚘 9 EUI-645</t>
+          <t>🚙 7 EUI-679</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NOCHE, DÍA, TARDE</t>
+          <t>DÍA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SECTORIAL</t>
+          <t>T.ALTA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FALTA 30 KM, COMPLETO, PO requerido</t>
+          <t>ENACE</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FALTA 45 KM, FALTA 20 MIN (1T), FALTAN 1 P.O.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>03:14:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🚘 10 EUI-647</t>
+          <t>🚘 9 EUI-645</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>TARDE</t>
@@ -726,40 +745,49 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FALTA 82 KM, FALTA 150 MIN (5T), PO requerido</t>
+          <t>ENACE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FALTA 45 KM, FALTA 30 MIN (1T), FALTAN 2 P.O.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>03:14:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🚘 11 EUI-668</t>
+          <t>🚘 10 EUI-647</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TARDE</t>
+          <t>NOCHE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -769,50 +797,64 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FALTA 78 KM, FALTA 170 MIN (6T), PO requerido</t>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>COMPLETO, FALTA 25 MIN (1T), COMPLETO (5 P.O.)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:30:57</t>
+          <t>03:14:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🚘 12 EUI-670</t>
+          <t>🚘 11 EUI-668</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NOCHE, DÍA, TARDE</t>
+          <t>DÍA, TARDE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SECTORIAL</t>
+          <t>T.ALTA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FALTA 13 KM, COMPLETO, PO requerido</t>
+          <t>SUR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
         </is>
       </c>
     </row>

--- a/mvc/dist/SerenazgoTalara/unidades_registro.xlsx
+++ b/mvc/dist/SerenazgoTalara/unidades_registro.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00366092"/>
         <bgColor rgb="00366092"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
-        <bgColor rgb="002C3E50"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,12 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -444,417 +435,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>HORA</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>KM</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TURNO</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>JURISDICCION</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>03:14:06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🚙 1 EUI-621</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NOCHE, DÍA, TARDE</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>03:14:06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🚙 2 EUI-682</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>DÍA, TARDE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>03:14:06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🚙 3 EUI-683</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>NOCHE, TARDE</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>T.ALTA</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SUR</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>03:14:06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🚙 7 EUI-679</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DÍA</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>T.ALTA</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ENACE</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>FALTA 45 KM, FALTA 20 MIN (1T), FALTAN 1 P.O.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>03:14:06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🚘 9 EUI-645</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TARDE</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>T.ALTA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ENACE</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>FALTA 45 KM, FALTA 30 MIN (1T), FALTAN 2 P.O.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>03:14:06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🚘 10 EUI-647</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>NOCHE</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>COMPLETO, FALTA 25 MIN (1T), COMPLETO (5 P.O.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>03:14:06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>🚘 11 EUI-668</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>DÍA, TARDE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>T.ALTA</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>SUR</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
         </is>
       </c>
     </row>

--- a/mvc/dist/SerenazgoTalara/unidades_registro.xlsx
+++ b/mvc/dist/SerenazgoTalara/unidades_registro.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -47,7 +44,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,19 +52,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/mvc/dist/SerenazgoTalara/unidades_registro.xlsx
+++ b/mvc/dist/SerenazgoTalara/unidades_registro.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -44,7 +47,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,13 +55,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
